--- a/artfynd/A 54346-2024 artfynd.xlsx
+++ b/artfynd/A 54346-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121307790</v>
       </c>
       <c r="B2" t="n">
-        <v>90707</v>
+        <v>90717</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>121370209</v>
       </c>
       <c r="B3" t="n">
-        <v>90707</v>
+        <v>90717</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>121369552</v>
       </c>
       <c r="B4" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 54346-2024 artfynd.xlsx
+++ b/artfynd/A 54346-2024 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121370209</v>
+        <v>121369552</v>
       </c>
       <c r="B3" t="n">
-        <v>90717</v>
+        <v>91973</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,30 +801,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578769</v>
+        <v>578792</v>
       </c>
       <c r="R3" t="n">
-        <v>6386450</v>
+        <v>6386487</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121369552</v>
+        <v>121370209</v>
       </c>
       <c r="B4" t="n">
-        <v>91973</v>
+        <v>90717</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,30 +915,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578792</v>
+        <v>578769</v>
       </c>
       <c r="R4" t="n">
-        <v>6386487</v>
+        <v>6386450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 54346-2024 artfynd.xlsx
+++ b/artfynd/A 54346-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121307790</v>
       </c>
       <c r="B2" t="n">
-        <v>90717</v>
+        <v>90729</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>121369552</v>
       </c>
       <c r="B3" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>121370209</v>
       </c>
       <c r="B4" t="n">
-        <v>90717</v>
+        <v>90729</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 54346-2024 artfynd.xlsx
+++ b/artfynd/A 54346-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121307790</v>
       </c>
       <c r="B2" t="n">
-        <v>90729</v>
+        <v>90730</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>121369552</v>
       </c>
       <c r="B3" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>121370209</v>
       </c>
       <c r="B4" t="n">
-        <v>90729</v>
+        <v>90730</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 54346-2024 artfynd.xlsx
+++ b/artfynd/A 54346-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121307790</v>
       </c>
       <c r="B2" t="n">
-        <v>90730</v>
+        <v>90733</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>121369552</v>
       </c>
       <c r="B3" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>121370209</v>
       </c>
       <c r="B4" t="n">
-        <v>90730</v>
+        <v>90733</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 54346-2024 artfynd.xlsx
+++ b/artfynd/A 54346-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121307790</v>
       </c>
       <c r="B2" t="n">
-        <v>90733</v>
+        <v>90739</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121369552</v>
+        <v>121370209</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
+        <v>90739</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,30 +801,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578792</v>
+        <v>578769</v>
       </c>
       <c r="R3" t="n">
-        <v>6386487</v>
+        <v>6386450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121370209</v>
+        <v>121369552</v>
       </c>
       <c r="B4" t="n">
-        <v>90733</v>
+        <v>91995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,30 +915,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578769</v>
+        <v>578792</v>
       </c>
       <c r="R4" t="n">
-        <v>6386450</v>
+        <v>6386487</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 54346-2024 artfynd.xlsx
+++ b/artfynd/A 54346-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121307790</v>
       </c>
       <c r="B2" t="n">
-        <v>90739</v>
+        <v>90740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121370209</v>
+        <v>121369552</v>
       </c>
       <c r="B3" t="n">
-        <v>90739</v>
+        <v>91996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,30 +801,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578769</v>
+        <v>578792</v>
       </c>
       <c r="R3" t="n">
-        <v>6386450</v>
+        <v>6386487</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121369552</v>
+        <v>121370209</v>
       </c>
       <c r="B4" t="n">
-        <v>91995</v>
+        <v>90740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,30 +915,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578792</v>
+        <v>578769</v>
       </c>
       <c r="R4" t="n">
-        <v>6386487</v>
+        <v>6386450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 54346-2024 artfynd.xlsx
+++ b/artfynd/A 54346-2024 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121369552</v>
+        <v>121370209</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
+        <v>90740</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,30 +801,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578792</v>
+        <v>578769</v>
       </c>
       <c r="R3" t="n">
-        <v>6386487</v>
+        <v>6386450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121370209</v>
+        <v>121369552</v>
       </c>
       <c r="B4" t="n">
-        <v>90740</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,30 +915,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578769</v>
+        <v>578792</v>
       </c>
       <c r="R4" t="n">
-        <v>6386450</v>
+        <v>6386487</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 54346-2024 artfynd.xlsx
+++ b/artfynd/A 54346-2024 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121370209</v>
+        <v>121369552</v>
       </c>
       <c r="B3" t="n">
-        <v>90740</v>
+        <v>91996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,30 +801,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578769</v>
+        <v>578792</v>
       </c>
       <c r="R3" t="n">
-        <v>6386450</v>
+        <v>6386487</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121369552</v>
+        <v>121370209</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>90740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,30 +915,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578792</v>
+        <v>578769</v>
       </c>
       <c r="R4" t="n">
-        <v>6386487</v>
+        <v>6386450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 54346-2024 artfynd.xlsx
+++ b/artfynd/A 54346-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121307790</v>
       </c>
       <c r="B2" t="n">
-        <v>90740</v>
+        <v>90748</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>121370209</v>
       </c>
       <c r="B3" t="n">
-        <v>90740</v>
+        <v>90748</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>121369552</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>92004</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
